--- a/jira_export_2026-08-10.xlsx
+++ b/jira_export_2026-08-10.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>368 €</t>
+          <t>1,003 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>636 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>92 h</t>
+          <t>98 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1190,32 +1190,32 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[Commune du Tampon] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N7" s="12" t="n">
-        <v>495</v>
+        <v>789.5</v>
       </c>
       <c r="O7" s="16" t="n">
         <v>0</v>
@@ -1262,12 +1262,12 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1302,27 +1302,27 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
-        <v>1892</v>
+        <v>495</v>
       </c>
       <c r="O8" s="16" t="n">
         <v>0</v>
@@ -1334,32 +1334,32 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>895</v>
+        <v>1892</v>
       </c>
       <c r="O9" s="16" t="n">
         <v>0</v>
@@ -1406,27 +1406,27 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00171711</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>50</v>
+        <v>895</v>
       </c>
       <c r="O10" s="16" t="n">
         <v>0</v>
@@ -1478,12 +1478,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -1529,16 +1529,16 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>769.5</v>
+        <v>50</v>
       </c>
       <c r="O11" s="16" t="n">
         <v>0</v>
@@ -1550,27 +1550,27 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
@@ -1601,16 +1601,16 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>2127.2</v>
+        <v>769.5</v>
       </c>
       <c r="O12" s="16" t="n">
         <v>0</v>
@@ -1622,32 +1622,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1657,32 +1657,32 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1694,32 +1694,32 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1729,35 +1729,35 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O14" s="16" t="n">
-        <v>367.5</v>
+        <v>0</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>0</v>
@@ -1766,12 +1766,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -1817,19 +1817,19 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O15" s="16" t="n">
-        <v>0</v>
+        <v>367.5</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
@@ -1838,27 +1838,27 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
@@ -1889,16 +1889,16 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1910,12 +1910,12 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1982,12 +1982,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
@@ -2033,16 +2033,16 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2054,27 +2054,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2126,32 +2126,32 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -2161,32 +2161,32 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2198,27 +2198,27 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2245,20 +2245,20 @@
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2270,32 +2270,32 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
@@ -2321,16 +2321,16 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>680</v>
+        <v>220</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2342,32 +2342,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2377,32 +2377,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>787.5</v>
+        <v>680</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2414,12 +2414,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2461,22 +2461,22 @@
         <v>2</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>8</v>
+        <v>0.25</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
@@ -2486,12 +2486,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2533,52 +2533,52 @@
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O25" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O25" s="12" t="n">
+        <v>416.29</v>
       </c>
       <c r="P25" s="12" t="n">
-        <v>0</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2609,16 +2609,16 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2630,32 +2630,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2681,16 +2681,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1616</v>
+        <v>920</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2702,27 +2702,27 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
@@ -2753,16 +2753,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>1017.5</v>
+        <v>1616</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2774,27 +2774,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2809,32 +2809,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1416</v>
+        <v>1017.5</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2846,32 +2846,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2897,16 +2897,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>171.4</v>
+        <v>1416</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2918,32 +2918,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2969,16 +2969,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>4174</v>
+        <v>171.4</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2990,27 +2990,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
@@ -3041,16 +3041,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>344</v>
+        <v>4174</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3062,32 +3062,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3113,16 +3113,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>514.2</v>
+        <v>344</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3134,32 +3134,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3185,16 +3185,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>500</v>
+        <v>514.2</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3206,27 +3206,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3257,16 +3257,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3278,32 +3278,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3313,32 +3313,32 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3401,18 +3401,18 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="12" t="n">
+        <v>625</v>
+      </c>
+      <c r="O37" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -3422,32 +3422,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3457,34 +3457,34 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3494,12 +3494,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3534,27 +3534,27 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3566,27 +3566,27 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3617,16 +3617,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>1079</v>
+        <v>1207</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3638,32 +3638,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3673,32 +3673,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>500</v>
+        <v>1079</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3710,32 +3710,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
@@ -3761,16 +3761,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3782,32 +3782,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3817,32 +3817,32 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1294.224</v>
+        <v>400</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3854,12 +3854,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3894,64 +3894,64 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>142.1</v>
+        <v>1294.224</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>0</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3998,27 +3998,27 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4049,16 +4049,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4070,32 +4070,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4105,32 +4105,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4142,28 +4142,32 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4173,32 +4177,32 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4210,27 +4214,23 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr"/>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4261,16 +4261,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>590.15</v>
+        <v>255</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4282,27 +4282,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4322,29 +4322,29 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="15" t="n">
@@ -4354,32 +4354,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4394,29 +4394,29 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="12" t="n">
+        <v>590.15</v>
+      </c>
+      <c r="O51" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="12" t="n">
@@ -4426,12 +4426,12 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4477,16 +4477,16 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>285</v>
+        <v>1000</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4498,12 +4498,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4533,34 +4533,34 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>1325</v>
-      </c>
-      <c r="O53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
@@ -4570,32 +4570,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4621,16 +4621,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4642,32 +4642,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4693,16 +4693,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>588</v>
+        <v>1325</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4714,32 +4714,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4749,32 +4749,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4786,27 +4786,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4826,27 +4826,27 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>300</v>
+        <v>588</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4858,32 +4858,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4893,32 +4893,32 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>700</v>
+        <v>203.5</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4930,61 +4930,69 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L59" s="11" t="inlineStr"/>
-      <c r="M59" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>00157967</t>
+        </is>
+      </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="O59" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -4994,27 +5002,27 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5034,27 +5042,27 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>416.475</v>
+        <v>700</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5066,69 +5074,61 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31360</t>
-        </is>
-      </c>
-      <c r="M61" s="11" t="inlineStr">
-        <is>
-          <t>00157041</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L61" s="11" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr"/>
       <c r="N61" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="O61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5138,32 +5138,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5189,16 +5189,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>281</v>
+        <v>416.475</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5210,12 +5210,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5261,16 +5261,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5282,12 +5282,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
@@ -5333,16 +5333,16 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5354,12 +5354,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -5394,27 +5394,27 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5426,32 +5426,32 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>690</v>
+        <v>255</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5498,32 +5498,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5549,16 +5549,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>187.5</v>
+        <v>140</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5570,27 +5570,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5610,27 +5610,27 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>787.5</v>
+        <v>690</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5642,32 +5642,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5677,32 +5677,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>725</v>
+        <v>187.5</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5714,27 +5714,27 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5749,34 +5749,34 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
@@ -5786,32 +5786,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5821,34 +5821,34 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O71" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
@@ -6053,18 +6053,18 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6074,12 +6074,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6089,11 +6089,13 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
@@ -6112,23 +6114,23 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6144,12 +6146,12 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -6159,11 +6161,13 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -6182,27 +6186,27 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>1212</v>
+        <v>1320</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6214,28 +6218,26 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v/>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
@@ -6254,23 +6256,23 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6286,12 +6288,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6301,13 +6303,11 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v/>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -6316,31 +6316,39 @@
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L78" s="14" t="inlineStr"/>
-      <c r="M78" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M78" s="14" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6350,12 +6358,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6365,11 +6373,13 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
@@ -6388,23 +6398,23 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K79" s="11" t="n">
         <v>0.25</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
@@ -6420,26 +6430,28 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -6448,35 +6460,27 @@
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27995</t>
-        </is>
-      </c>
-      <c r="M80" s="14" t="inlineStr">
-        <is>
-          <t>501218</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
       <c r="N80" s="15" t="n">
         <v>0</v>
       </c>
@@ -6490,22 +6494,22 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6528,23 +6532,23 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
@@ -6560,22 +6564,22 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
@@ -6598,23 +6602,23 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
@@ -6645,7 +6649,7 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -6679,12 +6683,12 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
@@ -6749,12 +6753,12 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6770,22 +6774,22 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -6803,34 +6807,34 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O85" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6840,12 +6844,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6855,7 +6859,7 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E86" s="14" t="n">
@@ -6871,20 +6875,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H86" s="14" t="inlineStr"/>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L86" s="14" t="inlineStr"/>
-      <c r="M86" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L86" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M86" s="14" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N86" s="15" t="n">
         <v>0</v>
       </c>
@@ -6898,12 +6914,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6913,7 +6929,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6931,34 +6947,34 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O87" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6968,22 +6984,22 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -6999,36 +7015,24 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H88" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H88" s="14" t="inlineStr"/>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>16</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M88" s="14" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L88" s="14" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
       <c r="N88" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7038,22 +7042,22 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -7066,23 +7070,35 @@
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H89" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L89" s="11" t="inlineStr"/>
-      <c r="M89" s="11" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M89" s="11" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N89" s="12" t="n">
         <v>0</v>
       </c>
@@ -7096,12 +7112,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7111,7 +7127,7 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
@@ -7124,31 +7140,39 @@
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr"/>
-      <c r="M90" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M90" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7158,22 +7182,22 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7181,44 +7205,32 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr"/>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M91" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L91" s="11" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr"/>
       <c r="N91" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7228,12 +7240,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7243,7 +7255,7 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7256,39 +7268,31 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M92" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L92" s="14" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
       <c r="N92" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7298,22 +7302,22 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7321,36 +7325,44 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L93" s="11" t="inlineStr"/>
-      <c r="M93" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O93" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7360,12 +7372,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7375,7 +7387,7 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7388,7 +7400,7 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H94" s="14" t="inlineStr">
@@ -7398,29 +7410,29 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7430,22 +7442,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7458,7 +7470,7 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
@@ -7468,25 +7480,17 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M95" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr"/>
       <c r="N95" s="12" t="n">
         <v>0</v>
       </c>
@@ -7500,22 +7504,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7533,28 +7537,28 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7570,12 +7574,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7585,13 +7589,11 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v/>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7600,7 +7602,7 @@
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -7610,17 +7612,25 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L97" s="11" t="inlineStr"/>
-      <c r="M97" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M97" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N97" s="12" t="n">
         <v>0</v>
       </c>
@@ -7634,24 +7644,26 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v/>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -7670,53 +7682,185 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K98" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M98" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="N98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K99" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L99" s="11" t="inlineStr"/>
+      <c r="M99" s="11" t="inlineStr"/>
+      <c r="N99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr"/>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J100" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K100" s="14" t="n">
         <v>1.5</v>
       </c>
-      <c r="L98" s="14" t="inlineStr"/>
-      <c r="M98" s="14" t="inlineStr"/>
-      <c r="N98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="17" t="inlineStr">
+      <c r="L100" s="14" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+      <c r="N100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B99" s="17" t="inlineStr"/>
-      <c r="C99" s="17" t="inlineStr"/>
-      <c r="D99" s="17" t="inlineStr"/>
-      <c r="E99" s="17" t="inlineStr"/>
-      <c r="F99" s="17" t="inlineStr"/>
-      <c r="G99" s="17" t="inlineStr"/>
-      <c r="H99" s="17" t="inlineStr"/>
-      <c r="I99" s="17" t="inlineStr"/>
-      <c r="J99" s="17" t="inlineStr"/>
-      <c r="K99" s="17" t="inlineStr"/>
-      <c r="L99" s="17" t="inlineStr"/>
-      <c r="M99" s="17" t="inlineStr"/>
-      <c r="N99" s="18" t="n">
-        <v>64154.894</v>
-      </c>
-      <c r="O99" s="18" t="n">
-        <v>367.5</v>
-      </c>
-      <c r="P99" s="18" t="n">
-        <v>7.46</v>
+      <c r="B101" s="17" t="inlineStr"/>
+      <c r="C101" s="17" t="inlineStr"/>
+      <c r="D101" s="17" t="inlineStr"/>
+      <c r="E101" s="17" t="inlineStr"/>
+      <c r="F101" s="17" t="inlineStr"/>
+      <c r="G101" s="17" t="inlineStr"/>
+      <c r="H101" s="17" t="inlineStr"/>
+      <c r="I101" s="17" t="inlineStr"/>
+      <c r="J101" s="17" t="inlineStr"/>
+      <c r="K101" s="17" t="inlineStr"/>
+      <c r="L101" s="17" t="inlineStr"/>
+      <c r="M101" s="17" t="inlineStr"/>
+      <c r="N101" s="18" t="n">
+        <v>64944.394</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>1003.15</v>
+      </c>
+      <c r="P101" s="18" t="n">
+        <v>18.15</v>
       </c>
     </row>
   </sheetData>
@@ -7816,6 +7960,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8390,16 +8536,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>38.5</v>
+        <v>42</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>49.25</v>
+        <v>53.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>8</v>
@@ -8409,7 +8555,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8566,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -8429,7 +8575,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -8439,7 +8585,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8597,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
     </row>
   </sheetData>
@@ -8536,16 +8682,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>388738</v>
+        <v>388102</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>146643</v>
+        <v>146424</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>242094</v>
+        <v>241678</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>151790</v>
+        <v>151374</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -8561,16 +8707,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>174704</v>
+        <v>174068</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>70979</v>
+        <v>70759</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>103725</v>
+        <v>103308</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>86309</v>
+        <v>85893</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>

--- a/jira_export_2026-08-10.xlsx
+++ b/jira_export_2026-08-10.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>98 h</t>
+          <t>119 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1054,37 +1054,37 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34848</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
+          <t>[COMMUNE DE PALAVAS-LES-FLOTS] - Ajout d'un Pax + Carte M2M + reinst apk et cb</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Marine MASINGARBE</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
+          <t>Ajout d'un Pax + Carte M2M + reinst apk et cb</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -1094,17 +1094,25 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="J5" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L5" s="11" t="inlineStr"/>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35008</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>00178436</t>
+        </is>
+      </c>
       <c r="N5" s="12" t="n">
         <v>0</v>
       </c>
@@ -1118,42 +1126,42 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34848</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Marine MASINGARBE</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
@@ -1165,22 +1173,14 @@
         <v>1</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34825</t>
-        </is>
-      </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>00177218</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="14" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
       <c r="N6" s="15" t="n">
-        <v>2419</v>
-      </c>
-      <c r="O6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="15" t="n">
@@ -1190,27 +1190,27 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[Commune du Tampon] - Migration GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N7" s="12" t="n">
-        <v>789.5</v>
+        <v>2419</v>
       </c>
       <c r="O7" s="16" t="n">
         <v>0</v>
@@ -1262,32 +1262,32 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - GEODP PLACIER</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
@@ -1313,16 +1313,16 @@
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
-        <v>495</v>
+        <v>429.3</v>
       </c>
       <c r="O8" s="16" t="n">
         <v>0</v>
@@ -1334,32 +1334,32 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[Commune du Tampon] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>1892</v>
+        <v>789.5</v>
       </c>
       <c r="O9" s="16" t="n">
         <v>0</v>
@@ -1406,32 +1406,32 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
@@ -1457,16 +1457,16 @@
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>895</v>
+        <v>495</v>
       </c>
       <c r="O10" s="16" t="n">
         <v>0</v>
@@ -1478,32 +1478,32 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1518,27 +1518,27 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00171711</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>50</v>
+        <v>1892</v>
       </c>
       <c r="O11" s="16" t="n">
         <v>0</v>
@@ -1550,27 +1550,27 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1590,27 +1590,27 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>769.5</v>
+        <v>895</v>
       </c>
       <c r="O12" s="16" t="n">
         <v>0</v>
@@ -1622,27 +1622,27 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
@@ -1673,16 +1673,16 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2127.2</v>
+        <v>50</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1694,32 +1694,32 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1729,32 +1729,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>4536</v>
+        <v>769.5</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1766,27 +1766,27 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
@@ -1817,19 +1817,19 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>525</v>
+        <v>2127.2</v>
       </c>
       <c r="O15" s="16" t="n">
-        <v>367.5</v>
+        <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
@@ -1838,32 +1838,32 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1873,32 +1873,32 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>1662</v>
+        <v>4536</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1910,27 +1910,27 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1961,19 +1961,19 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>9623.1</v>
+        <v>525</v>
       </c>
       <c r="O17" s="16" t="n">
-        <v>0</v>
+        <v>367.5</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
@@ -1982,27 +1982,27 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
@@ -2033,16 +2033,16 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>707</v>
+        <v>1662</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2054,12 +2054,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>300</v>
+        <v>9623.1</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2126,27 +2126,27 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
@@ -2177,16 +2177,16 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>510</v>
+        <v>707</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2198,32 +2198,32 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>242.9</v>
+        <v>300</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2270,32 +2270,32 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
@@ -2321,16 +2321,16 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2342,32 +2342,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2377,32 +2377,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>680</v>
+        <v>242.9</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2414,12 +2414,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2454,27 +2454,27 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>787.5</v>
+        <v>220</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2486,32 +2486,32 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2521,69 +2521,69 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>8.25</v>
+        <v>0.25</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>416.29</v>
+        <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
-        <v>50.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2609,16 +2609,16 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>1890</v>
+        <v>680</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2630,27 +2630,27 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2670,27 +2670,27 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>920</v>
+        <v>787.5</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2702,32 +2702,32 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2737,69 +2737,69 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>1616</v>
-      </c>
-      <c r="O28" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O28" s="15" t="n">
+        <v>416.29</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>0</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2825,16 +2825,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1017.5</v>
+        <v>1890</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2846,32 +2846,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2881,32 +2881,32 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>1416</v>
+        <v>920</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2918,32 +2918,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2953,32 +2953,32 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>171.4</v>
+        <v>1616</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2990,27 +2990,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3025,32 +3025,32 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>4174</v>
+        <v>1017.5</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3062,27 +3062,27 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3113,16 +3113,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>344</v>
+        <v>1416</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3134,12 +3134,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3185,16 +3185,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>514.2</v>
+        <v>171.4</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3206,12 +3206,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3257,16 +3257,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>500</v>
+        <v>4174</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3278,12 +3278,12 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
@@ -3329,16 +3329,16 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>149</v>
+        <v>344</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3350,27 +3350,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3390,27 +3390,27 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>625</v>
+        <v>514.2</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3422,32 +3422,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3462,29 +3462,29 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3494,12 +3494,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3534,27 +3534,27 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>910</v>
+        <v>149</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3566,32 +3566,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>1207</v>
+        <v>625</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3638,32 +3638,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3673,34 +3673,34 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1079</v>
-      </c>
-      <c r="O41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="12" t="n">
@@ -3710,32 +3710,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3782,12 +3782,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3833,16 +3833,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>400</v>
+        <v>1207</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3854,32 +3854,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3889,64 +3889,64 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>2.25</v>
+        <v>0.25</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>1294.224</v>
+        <v>1079</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>97.48999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3977,16 +3977,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>142.1</v>
+        <v>500</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3998,27 +3998,27 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4038,27 +4038,27 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>2335</v>
+        <v>400</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4070,32 +4070,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4105,64 +4105,64 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>450</v>
+        <v>1294.224</v>
       </c>
       <c r="O47" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>0</v>
+        <v>87.73999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4182,27 +4182,27 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>910</v>
+        <v>142.1</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4214,23 +4214,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr"/>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4250,7 +4254,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4261,16 +4265,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>255</v>
+        <v>2335</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4282,27 +4286,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4322,29 +4326,29 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="O50" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="15" t="n">
@@ -4354,32 +4358,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4389,32 +4393,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4426,27 +4430,23 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr"/>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4477,16 +4477,16 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>1000</v>
+        <v>255</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4498,32 +4498,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4533,28 +4533,28 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
@@ -4570,12 +4570,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4621,16 +4621,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4642,32 +4642,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4693,16 +4693,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1325</v>
+        <v>1000</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4714,12 +4714,12 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4749,34 +4749,34 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="O56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
@@ -4786,12 +4786,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4837,16 +4837,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>588</v>
+        <v>285</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4858,32 +4858,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4893,32 +4893,32 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>203.5</v>
+        <v>1325</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4930,32 +4930,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -5002,32 +5002,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5037,32 +5037,32 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>700</v>
+        <v>588</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5074,61 +5074,69 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L61" s="11" t="inlineStr"/>
-      <c r="M61" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31658</t>
+        </is>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>00158175</t>
+        </is>
+      </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5138,32 +5146,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5173,12 +5181,12 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5189,16 +5197,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>416.475</v>
+        <v>300</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5210,32 +5218,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5245,32 +5253,32 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5282,69 +5290,61 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31328</t>
-        </is>
-      </c>
-      <c r="M64" s="14" t="inlineStr">
-        <is>
-          <t>00156518</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
       <c r="N64" s="15" t="n">
-        <v>281</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5354,32 +5354,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5405,16 +5405,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>130</v>
+        <v>416.475</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5426,12 +5426,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5477,16 +5477,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5498,12 +5498,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5538,27 +5538,27 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>140</v>
+        <v>281</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5570,32 +5570,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5605,32 +5605,32 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>690</v>
+        <v>130</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5642,32 +5642,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5677,32 +5677,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>187.5</v>
+        <v>255</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5714,32 +5714,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
@@ -5765,16 +5765,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>787.5</v>
+        <v>140</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5786,32 +5786,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>725</v>
+        <v>690</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5858,27 +5858,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5893,34 +5893,34 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5930,27 +5930,27 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5965,34 +5965,34 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O73" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -6002,32 +6002,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6037,34 +6037,34 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
+        <v>725</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6197,18 +6197,18 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6218,12 +6218,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6233,11 +6233,13 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
@@ -6256,23 +6258,23 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6288,12 +6290,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6303,11 +6305,13 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -6326,29 +6330,29 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O78" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6358,22 +6362,22 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -6398,29 +6402,29 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O79" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6430,12 +6434,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6445,13 +6449,11 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v/>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -6460,27 +6462,35 @@
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr"/>
-      <c r="M80" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M80" s="14" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
       <c r="N80" s="15" t="n">
         <v>0</v>
       </c>
@@ -6494,22 +6504,22 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6532,29 +6542,29 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O81" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6564,12 +6574,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -6579,11 +6589,13 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -6602,23 +6614,23 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
@@ -6634,12 +6646,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6649,11 +6661,13 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
@@ -6662,35 +6676,27 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30081</t>
-        </is>
-      </c>
-      <c r="M83" s="11" t="inlineStr">
-        <is>
-          <t>00152628</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
       <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
@@ -6704,22 +6710,22 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
@@ -6742,23 +6748,23 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6774,22 +6780,22 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -6812,23 +6818,23 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
@@ -6893,12 +6899,12 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6914,22 +6920,22 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6947,34 +6953,34 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O87" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6984,12 +6990,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -6999,7 +7005,7 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -7015,20 +7021,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H88" s="14" t="inlineStr"/>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L88" s="14" t="inlineStr"/>
-      <c r="M88" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L88" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-30079</t>
+        </is>
+      </c>
+      <c r="M88" s="14" t="inlineStr">
+        <is>
+          <t>00152632</t>
+        </is>
+      </c>
       <c r="N88" s="15" t="n">
         <v>0</v>
       </c>
@@ -7042,22 +7060,22 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -7080,23 +7098,23 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
@@ -7112,12 +7130,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7127,7 +7145,7 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
@@ -7150,27 +7168,27 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K90" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>230</v>
+        <v>401</v>
       </c>
       <c r="O90" s="16" t="n">
         <v>0</v>
@@ -7182,12 +7200,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7197,7 +7215,7 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7210,20 +7228,20 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr"/>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L91" s="11" t="inlineStr"/>
       <c r="M91" s="11" t="inlineStr"/>
@@ -7240,12 +7258,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7255,7 +7273,7 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7268,7 +7286,7 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
@@ -7278,17 +7296,25 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L92" s="14" t="inlineStr"/>
-      <c r="M92" s="14" t="inlineStr"/>
+        <v>3.75</v>
+      </c>
+      <c r="L92" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M92" s="14" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N92" s="15" t="n">
         <v>0</v>
       </c>
@@ -7302,22 +7328,22 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7325,7 +7351,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7335,32 +7361,32 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K93" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O93" s="16" t="n">
         <v>0</v>
@@ -7372,22 +7398,22 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7400,39 +7426,27 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr"/>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M94" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L94" s="14" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
       <c r="N94" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O94" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7442,22 +7456,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7475,19 +7489,19 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L95" s="11" t="inlineStr"/>
       <c r="M95" s="11" t="inlineStr"/>
@@ -7504,22 +7518,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7527,44 +7541,44 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
@@ -7574,12 +7588,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7589,7 +7603,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7612,29 +7626,29 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O97" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7644,12 +7658,12 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -7659,7 +7673,7 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7677,30 +7691,22 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M98" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L98" s="14" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
       <c r="N98" s="15" t="n">
         <v>0</v>
       </c>
@@ -7714,12 +7720,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7729,13 +7735,11 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v/>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
@@ -7754,17 +7758,25 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L99" s="11" t="inlineStr"/>
-      <c r="M99" s="11" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N99" s="12" t="n">
         <v>0</v>
       </c>
@@ -7778,24 +7790,26 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C100" s="14" t="inlineStr"/>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E100" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="n">
+        <v/>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -7804,63 +7818,265 @@
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K100" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M100" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12666</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>19/09/2023</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K101" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="N101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K102" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L102" s="14" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+      <c r="N102" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr"/>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K103" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="L100" s="14" t="inlineStr"/>
-      <c r="M100" s="14" t="inlineStr"/>
-      <c r="N100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="17" t="inlineStr">
+      <c r="L103" s="11" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr"/>
+      <c r="N103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B101" s="17" t="inlineStr"/>
-      <c r="C101" s="17" t="inlineStr"/>
-      <c r="D101" s="17" t="inlineStr"/>
-      <c r="E101" s="17" t="inlineStr"/>
-      <c r="F101" s="17" t="inlineStr"/>
-      <c r="G101" s="17" t="inlineStr"/>
-      <c r="H101" s="17" t="inlineStr"/>
-      <c r="I101" s="17" t="inlineStr"/>
-      <c r="J101" s="17" t="inlineStr"/>
-      <c r="K101" s="17" t="inlineStr"/>
-      <c r="L101" s="17" t="inlineStr"/>
-      <c r="M101" s="17" t="inlineStr"/>
-      <c r="N101" s="18" t="n">
-        <v>64944.394</v>
-      </c>
-      <c r="O101" s="18" t="n">
+      <c r="B104" s="17" t="inlineStr"/>
+      <c r="C104" s="17" t="inlineStr"/>
+      <c r="D104" s="17" t="inlineStr"/>
+      <c r="E104" s="17" t="inlineStr"/>
+      <c r="F104" s="17" t="inlineStr"/>
+      <c r="G104" s="17" t="inlineStr"/>
+      <c r="H104" s="17" t="inlineStr"/>
+      <c r="I104" s="17" t="inlineStr"/>
+      <c r="J104" s="17" t="inlineStr"/>
+      <c r="K104" s="17" t="inlineStr"/>
+      <c r="L104" s="17" t="inlineStr"/>
+      <c r="M104" s="17" t="inlineStr"/>
+      <c r="N104" s="18" t="n">
+        <v>65373.694</v>
+      </c>
+      <c r="O104" s="18" t="n">
         <v>1003.15</v>
       </c>
-      <c r="P101" s="18" t="n">
-        <v>18.15</v>
+      <c r="P104" s="18" t="n">
+        <v>15.43</v>
       </c>
     </row>
   </sheetData>
@@ -7962,6 +8178,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8536,7 +8755,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>10.5</v>
@@ -8545,17 +8764,17 @@
         <v>0.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>53.25</v>
+        <v>62.25</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8785,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -8575,7 +8794,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -8585,7 +8804,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8816,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>35.25</v>
+        <v>38.25</v>
       </c>
     </row>
   </sheetData>
@@ -8682,10 +8901,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>388102</v>
+        <v>389245</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>146424</v>
+        <v>147567</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>241678</v>
@@ -8707,10 +8926,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>174068</v>
+        <v>174711</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>70759</v>
+        <v>71402</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>103308</v>
@@ -8732,10 +8951,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>214034</v>
+        <v>214534</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>75665</v>
+        <v>76165</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>138370</v>
@@ -8761,7 +8980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -8785,7 +9004,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 5 commande(s)</t>
+          <t>Épics créées ce mois — 6 commande(s)</t>
         </is>
       </c>
     </row>
@@ -8840,22 +9059,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -8875,37 +9094,37 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>4050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -8920,32 +9139,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>1500</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -8965,22 +9184,22 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -8990,7 +9209,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -9010,83 +9229,107 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I9" s="25" t="n">
+      <c r="I10" s="26" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>5 commande(s)</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="n">
-        <v>10050</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B11" s="17" t="n"/>
@@ -9097,17 +9340,17 @@
       <c r="G11" s="17" t="n"/>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>4 commande(s)</t>
+          <t>6 commande(s)</t>
         </is>
       </c>
       <c r="I11" s="24" t="n">
-        <v>6000</v>
+        <v>10550</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B12" s="17" t="n"/>
@@ -9118,11 +9361,32 @@
       <c r="G12" s="17" t="n"/>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>4 commande(s)</t>
         </is>
       </c>
       <c r="I12" s="24" t="n">
-        <v>4050</v>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>2 commande(s)</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>4550</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-10.xlsx
+++ b/jira_export_2026-08-10.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>119 h</t>
+          <t>128 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2054,69 +2054,61 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
       <c r="N19" s="12" t="n">
-        <v>9623.1</v>
-      </c>
-      <c r="O19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="12" t="n">
@@ -2126,12 +2118,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2141,12 +2133,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2166,7 +2158,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
@@ -2177,16 +2169,16 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2198,12 +2190,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2213,12 +2205,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2233,32 +2225,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2270,27 +2262,27 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2305,32 +2297,32 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2342,32 +2334,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2377,32 +2369,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2414,27 +2406,27 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2461,20 +2453,20 @@
         <v>2</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2486,32 +2478,32 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2521,34 +2513,34 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="O25" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
@@ -2558,27 +2550,27 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2605,22 +2597,22 @@
         <v>2</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>680</v>
-      </c>
-      <c r="O26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
@@ -2630,32 +2622,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2665,32 +2657,32 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>787.5</v>
+        <v>680</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2702,12 +2694,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -2717,12 +2709,12 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2749,37 +2741,37 @@
         <v>2</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>8.25</v>
+        <v>0.75</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="15" t="n">
-        <v>416.29</v>
+        <v>787.5</v>
+      </c>
+      <c r="O28" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>50.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2789,12 +2781,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2821,52 +2813,52 @@
         <v>2</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O29" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O29" s="12" t="n">
+        <v>416.29</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>0</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2886,7 +2878,7 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2897,16 +2889,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2918,32 +2910,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2953,12 +2945,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2969,16 +2961,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1616</v>
+        <v>920</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2990,27 +2982,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3025,7 +3017,7 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
@@ -3041,16 +3033,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>1017.5</v>
+        <v>1616</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3062,27 +3054,27 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3097,32 +3089,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1416</v>
+        <v>1017.5</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3134,32 +3126,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3169,12 +3161,12 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3185,16 +3177,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>171.4</v>
+        <v>1416</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3206,32 +3198,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3241,12 +3233,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3257,16 +3249,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>4174</v>
+        <v>171.4</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3278,27 +3270,27 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3313,12 +3305,12 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
@@ -3329,16 +3321,16 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>344</v>
+        <v>4174</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3350,32 +3342,32 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3397,20 +3389,20 @@
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>514.2</v>
+        <v>344</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3422,32 +3414,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3462,27 +3454,27 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>500</v>
+        <v>514.2</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3494,27 +3486,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3529,12 +3521,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3545,16 +3537,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3566,32 +3558,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3601,32 +3593,32 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3685,22 +3677,22 @@
         <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="12" t="n">
+        <v>625</v>
+      </c>
+      <c r="O41" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="12" t="n">
@@ -3710,32 +3702,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3745,34 +3737,34 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="15" t="n">
@@ -3782,12 +3774,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3797,12 +3789,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3822,27 +3814,27 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3854,27 +3846,27 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3894,27 +3886,27 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>1079</v>
+        <v>1207</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3926,32 +3918,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3961,32 +3953,32 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>500</v>
+        <v>1079</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3998,32 +3990,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4033,7 +4025,7 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -4049,16 +4041,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4070,32 +4062,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4105,49 +4097,49 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1294.224</v>
+        <v>400</v>
       </c>
       <c r="O47" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>87.73999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4157,12 +4149,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4182,64 +4174,64 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>142.1</v>
+        <v>1294.224</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>0</v>
+        <v>87.73999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4249,32 +4241,32 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4286,27 +4278,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4326,7 +4318,7 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4337,16 +4329,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4358,32 +4350,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4393,32 +4385,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4430,28 +4422,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4461,32 +4457,32 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4498,27 +4494,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr"/>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4545,22 +4537,22 @@
         <v>5</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="O53" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
@@ -4570,27 +4562,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4605,34 +4597,34 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
@@ -4642,12 +4634,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4657,12 +4649,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4677,12 +4669,12 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4693,16 +4685,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1000</v>
+        <v>590.15</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4714,32 +4706,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4749,34 +4741,34 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
@@ -4786,32 +4778,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4821,34 +4813,34 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4858,32 +4850,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4898,7 +4890,7 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
@@ -4909,16 +4901,16 @@
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4930,12 +4922,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4945,12 +4937,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4970,7 +4962,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4981,16 +4973,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -5002,32 +4994,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5037,7 +5029,7 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -5053,16 +5045,16 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5074,27 +5066,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5109,32 +5101,32 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O61" s="16" t="n">
         <v>0</v>
@@ -5146,12 +5138,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5161,12 +5153,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5181,12 +5173,12 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5197,16 +5189,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5218,32 +5210,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5253,32 +5245,32 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5290,12 +5282,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5305,12 +5297,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5320,7 +5312,7 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr">
@@ -5337,14 +5329,22 @@
         <v>6</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr"/>
-      <c r="M64" s="14" t="inlineStr"/>
+        <v>5.25</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5354,27 +5354,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -5394,29 +5394,21 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M65" s="11" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L65" s="11" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr"/>
       <c r="N65" s="12" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5426,32 +5418,32 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5461,12 +5453,12 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5477,16 +5469,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5498,12 +5490,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5513,12 +5505,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5549,16 +5541,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5570,12 +5562,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5585,12 +5577,12 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5610,7 +5602,7 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
@@ -5621,16 +5613,16 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5642,12 +5634,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5657,12 +5649,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5682,7 +5674,7 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5693,16 +5685,16 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5714,12 +5706,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5729,12 +5721,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5754,27 +5746,27 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K70" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5786,32 +5778,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5821,32 +5813,32 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5858,27 +5850,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5898,27 +5890,27 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5981,16 +5973,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -6002,32 +5994,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6037,32 +6029,32 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K74" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6074,32 +6066,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6109,34 +6101,34 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O75" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6197,12 +6189,12 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
@@ -6269,12 +6261,12 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6341,12 +6333,12 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
@@ -6413,18 +6405,18 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O79" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6434,12 +6426,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6449,11 +6441,13 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -6472,29 +6466,29 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6504,12 +6498,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6519,7 +6513,7 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6542,29 +6536,29 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O81" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6574,28 +6568,26 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E82" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v/>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
@@ -6614,29 +6606,29 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6646,27 +6638,27 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6676,27 +6668,35 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L83" s="11" t="inlineStr"/>
-      <c r="M83" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
@@ -6710,26 +6710,28 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -6738,35 +6740,27 @@
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L84" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M84" s="14" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L84" s="14" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
       <c r="N84" s="15" t="n">
         <v>0</v>
       </c>
@@ -6829,12 +6823,12 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
@@ -6850,22 +6844,22 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E86" s="14" t="n">
@@ -6888,23 +6882,23 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6969,12 +6963,12 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -7005,7 +6999,7 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -7039,12 +7033,12 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7075,7 +7069,7 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -7109,12 +7103,12 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
@@ -7130,22 +7124,22 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
@@ -7163,34 +7157,34 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7200,22 +7194,22 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7231,24 +7225,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H91" s="11" t="inlineStr"/>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L91" s="11" t="inlineStr"/>
-      <c r="M91" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M91" s="11" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O91" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7258,22 +7264,22 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7289,11 +7295,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H92" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H92" s="14" t="inlineStr"/>
       <c r="I92" s="14" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -7303,18 +7305,10 @@
         <v>16</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L92" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M92" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L92" s="14" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
       <c r="N92" s="15" t="n">
         <v>0</v>
       </c>
@@ -7328,12 +7322,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7343,7 +7337,7 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7361,34 +7355,34 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O93" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7398,22 +7392,22 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7426,27 +7420,39 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L94" s="14" t="inlineStr"/>
-      <c r="M94" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L94" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M94" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7456,22 +7462,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7487,21 +7493,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H95" s="11" t="inlineStr"/>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L95" s="11" t="inlineStr"/>
       <c r="M95" s="11" t="inlineStr"/>
@@ -7518,22 +7520,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7541,7 +7543,7 @@
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -7551,34 +7553,34 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
@@ -7588,12 +7590,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7603,7 +7605,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7616,39 +7618,31 @@
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M97" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L97" s="11" t="inlineStr"/>
+      <c r="M97" s="11" t="inlineStr"/>
       <c r="N97" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7658,22 +7652,22 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7681,36 +7675,44 @@
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L98" s="14" t="inlineStr"/>
-      <c r="M98" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L98" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M98" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
@@ -7720,12 +7722,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7735,7 +7737,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7748,7 +7750,7 @@
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
@@ -7758,29 +7760,29 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O99" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7790,22 +7792,22 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7818,7 +7820,7 @@
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr">
@@ -7828,25 +7830,17 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M100" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L100" s="14" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
       <c r="N100" s="15" t="n">
         <v>0</v>
       </c>
@@ -7860,22 +7854,22 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7893,28 +7887,28 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -7930,12 +7924,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -7945,13 +7939,11 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v/>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -7960,7 +7952,7 @@
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H102" s="14" t="inlineStr">
@@ -7970,17 +7962,25 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L102" s="14" t="inlineStr"/>
-      <c r="M102" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L102" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M102" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N102" s="15" t="n">
         <v>0</v>
       </c>
@@ -7994,24 +7994,26 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C103" s="11" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v/>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
@@ -8030,53 +8032,185 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K103" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="N103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K104" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+      <c r="N104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr"/>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K105" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="L103" s="11" t="inlineStr"/>
-      <c r="M103" s="11" t="inlineStr"/>
-      <c r="N103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="17" t="inlineStr">
+      <c r="L105" s="11" t="inlineStr"/>
+      <c r="M105" s="11" t="inlineStr"/>
+      <c r="N105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B104" s="17" t="inlineStr"/>
-      <c r="C104" s="17" t="inlineStr"/>
-      <c r="D104" s="17" t="inlineStr"/>
-      <c r="E104" s="17" t="inlineStr"/>
-      <c r="F104" s="17" t="inlineStr"/>
-      <c r="G104" s="17" t="inlineStr"/>
-      <c r="H104" s="17" t="inlineStr"/>
-      <c r="I104" s="17" t="inlineStr"/>
-      <c r="J104" s="17" t="inlineStr"/>
-      <c r="K104" s="17" t="inlineStr"/>
-      <c r="L104" s="17" t="inlineStr"/>
-      <c r="M104" s="17" t="inlineStr"/>
-      <c r="N104" s="18" t="n">
+      <c r="B106" s="17" t="inlineStr"/>
+      <c r="C106" s="17" t="inlineStr"/>
+      <c r="D106" s="17" t="inlineStr"/>
+      <c r="E106" s="17" t="inlineStr"/>
+      <c r="F106" s="17" t="inlineStr"/>
+      <c r="G106" s="17" t="inlineStr"/>
+      <c r="H106" s="17" t="inlineStr"/>
+      <c r="I106" s="17" t="inlineStr"/>
+      <c r="J106" s="17" t="inlineStr"/>
+      <c r="K106" s="17" t="inlineStr"/>
+      <c r="L106" s="17" t="inlineStr"/>
+      <c r="M106" s="17" t="inlineStr"/>
+      <c r="N106" s="18" t="n">
         <v>65373.694</v>
       </c>
-      <c r="O104" s="18" t="n">
+      <c r="O106" s="18" t="n">
         <v>1003.15</v>
       </c>
-      <c r="P104" s="18" t="n">
-        <v>15.43</v>
+      <c r="P106" s="18" t="n">
+        <v>14.33</v>
       </c>
     </row>
   </sheetData>
@@ -8181,6 +8315,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8755,16 +8891,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>51</v>
+        <v>55.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>10.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>62.25</v>
+        <v>67.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>16</v>
@@ -8774,7 +8910,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8952,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>38.25</v>
+        <v>41.75</v>
       </c>
     </row>
   </sheetData>
